--- a/Codelist Excel Files and Conversion Templates to XML/settlementEfficacyDefinition.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/settlementEfficacyDefinition.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes for which definition a diggs:RISystemDesignType/diggs:settlementEfficacy value uses. UNLIKE loadEfficacyDefinition, this vocabulary is NOT drawn from an explicit list in the schema's own documentation - the two entries here are standard ground-improvement settlement-ratio definitions proposed as a reasonable starting set, not a verbatim citation. Flagged for SME confirmation before relying on this list as closed, the same caveat this project already attaches to diggs:archingModel and diggs:measurementKind. Used for the value of diggs:RISystemDesignType/diggs:settlementEfficacyDefinition.</t>
+          <t>Codes for which definition a diggs:RITreatedAreaDesignType/diggs:settlementEfficacy value uses. UNLIKE loadEfficacyDefinition, this vocabulary is NOT drawn from an explicit list in the schema's own documentation - the two entries here are standard ground-improvement settlement-ratio definitions proposed as a reasonable starting set, not a verbatim citation. Flagged for SME confirmation before relying on this list as closed, the same caveat this project already attaches to diggs:archingModel and diggs:measurementKind. Used for the value of diggs:RITreatedAreaDesignType/diggs:settlementEfficacyDefinition.</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RISystemDesign/diggs:settlementEfficacyDefinition</t>
+          <t>//diggs:RITreatedAreaDesign/diggs:settlementEfficacyDefinition</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RISystemDesign/diggs:settlementEfficacyDefinition</t>
+          <t>//diggs:RITreatedAreaDesign/diggs:settlementEfficacyDefinition</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/settlementEfficacyDefinition.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/settlementEfficacyDefinition.xlsx
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>Settlement efficacy as the ratio of treated-ground settlement to untreated-ground settlement (values below 1 indicate improvement).</t>
+          <t>Efficacy expressed as the ratio of treated to untreated surface settlement, the complement of settlement_reduction_ratio, so that a smaller value means a more effective treatment. Complement of the ASIRI Eq 2.23 definition; see the DIGGS rigid inclusions technical report, Section 3.4.2 (Eq 3-11).</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>Settlement efficacy as one minus the settlement ratio - the fraction of untreated-ground settlement eliminated by treatment.</t>
+          <t>Efficacy expressed as the fractional reduction of surface settlement relative to the untreated soil, so that a larger value means a more effective treatment. ASIRI Eq 2.23, p. 79; confirmed against the DIGGS rigid inclusions technical report, Section 3.4.2 (Eq 3-11).</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
